--- a/jde_playwright_automation/test_data/ShippingData_JDE.xlsx
+++ b/jde_playwright_automation/test_data/ShippingData_JDE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\struts_playwright_automation\jde_playwright_automation\test_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{305F8D07-3097-44C6-A14A-33951F1810BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A954D34E-E636-42C2-BE61-D0308A8B9992}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="590" xr2:uid="{82038ABE-7B8C-4146-9485-918A215A8E15}"/>
   </bookViews>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="L63" s="1"/>
       <c r="M63" s="1" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="N63" s="1"/>
       <c r="O63" s="1"/>

--- a/jde_playwright_automation/test_data/ShippingData_JDE.xlsx
+++ b/jde_playwright_automation/test_data/ShippingData_JDE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\struts_playwright_automation\jde_playwright_automation\test_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A954D34E-E636-42C2-BE61-D0308A8B9992}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8837FDFF-EDF5-441F-A6E7-6F9D0CB7D64C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="590" xr2:uid="{82038ABE-7B8C-4146-9485-918A215A8E15}"/>
   </bookViews>
@@ -8043,7 +8043,7 @@
       </c>
       <c r="L61" s="1"/>
       <c r="M61" s="1" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="N61" s="1"/>
       <c r="O61" s="1"/>
@@ -8986,7 +8986,7 @@
       </c>
       <c r="L70" s="1"/>
       <c r="M70" s="1" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="N70" s="1" t="s">
         <v>41</v>
